--- a/ai-invest/templates/AI投資管理シート_テンプレート.xlsx
+++ b/ai-invest/templates/AI投資管理シート_テンプレート.xlsx
@@ -457,7 +457,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
@@ -536,7 +536,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A_内需安定</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A_内需安定</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A_内需安定</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B_IT・DX</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B_IT・DX</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B_IT・DX</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B_IT・DX</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C_製造・精密</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C_製造・精密</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C_製造・精密</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C_製造・精密</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D_医療</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D_医療</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D_医療</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E_金融</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>E_金融</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="D2:D201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" prompt="リストから選択してください" type="list">
-      <formula1>"A,B,C,D,E,TBD"</formula1>
+      <formula1>"A_内需安定,B_IT・DX,C_製造・精密,D_医療,E_金融,TBD"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E201" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" prompt="リストから選択してください" type="list">
       <formula1>"AI_UNIVERSE,AI_SCREENING,AI_NEWS,MANUAL_USER"</formula1>
@@ -3528,7 +3528,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -13640,7 +13640,7 @@
   </sheetData>
   <dataValidations count="11">
     <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" prompt="リストから選択してください" type="list">
-      <formula1>"A,B,C,D,E"</formula1>
+      <formula1>"A_内需安定,B_IT・DX,C_製造・精密,D_医療,E_金融"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" prompt="リストから選択してください" type="list">
       <formula1>"○,✕"</formula1>
@@ -23808,7 +23808,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -33396,7 +33396,7 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" prompt="リストから選択してください" type="list">
-      <formula1>"A,B,C,D,E"</formula1>
+      <formula1>"A_内需安定,B_IT・DX,C_製造・精密,D_医療,E_金融"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="入力エラー" error="リストから選択してください" prompt="リストから選択してください" type="list">
       <formula1>"25日線上の押し目,75日線上抜け後の初押し,高値更新ブレイク,出来高を伴うボックス上抜け,決算後ギャップアップ継続,25日線割れ反発失敗,その他"</formula1>
